--- a/results/Metrics.xlsx
+++ b/results/Metrics.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bavra\Desktop\image-unbluring\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7141DBD-A8C2-48FE-AAB1-534C89726EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254BCF37-35D0-4843-8EE2-72A9515DDEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9E8781EB-8CA8-4CA7-9ABE-25F10890F6BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9E8781EB-8CA8-4CA7-9ABE-25F10890F6BB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gauss-Seidel" sheetId="2" r:id="rId1"/>
-    <sheet name="Jacobi" sheetId="1" r:id="rId2"/>
+    <sheet name="Jacobi" sheetId="5" r:id="rId1"/>
+    <sheet name="Gauss-Seidel" sheetId="4" r:id="rId2"/>
+    <sheet name="SOR" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="3">
   <si>
     <t>Number of Iterations</t>
   </si>
   <si>
     <t>MSE</t>
+  </si>
+  <si>
+    <t>Omega</t>
   </si>
 </sst>
 </file>
@@ -64,15 +68,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -91,8 +93,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -101,8 +109,23 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
@@ -115,96 +138,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="4">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-      </border>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -239,27 +217,13 @@
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
+            <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -267,20 +231,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>MSE by Number Of Iterations (Gauss-Seidel)</a:t>
+              <a:rPr lang="en-GB"/>
+              <a:t>MSE by</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t> </a:t>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Number of Iterations (Jacobi Method)</a:t>
             </a:r>
+            <a:endParaRPr lang="en-GB"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -296,27 +254,13 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
+          <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:sysClr>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -339,7 +283,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Gauss-Seidel'!$B$1</c:f>
+              <c:f>Jacobi!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -350,7 +294,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -388,7 +332,6 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -418,7 +361,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Gauss-Seidel'!$A$2:$A$6</c:f>
+              <c:f>Jacobi!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -442,38 +385,37 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gauss-Seidel'!$B$2:$B$6</c:f>
+              <c:f>Jacobi!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>45.213999999999999</c:v>
+                  <c:v>42.866999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58.094999999999999</c:v>
+                  <c:v>48.762999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>64.718000000000004</c:v>
+                  <c:v>54.674999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>68.376000000000005</c:v>
+                  <c:v>59.201000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>70.561000000000007</c:v>
+                  <c:v>62.613</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A242-4499-BC67-D30FC3C8FD81}"/>
+              <c16:uniqueId val="{00000000-FC81-4861-9A96-97B8CA84C857}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -481,71 +423,16 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="165858447"/>
-        <c:axId val="165854127"/>
+        <c:axId val="365176239"/>
+        <c:axId val="365191119"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="165858447"/>
+        <c:axId val="365176239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Number of Iterations</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -583,7 +470,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="165854127"/>
+        <c:crossAx val="365191119"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -591,7 +478,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="165854127"/>
+        <c:axId val="365191119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -611,66 +498,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Mean</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" baseline="0"/>
-                  <a:t> Squared Error (MSE)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -702,7 +529,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="165858447"/>
+        <c:crossAx val="365176239"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -785,14 +612,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>MSE b</a:t>
+              <a:rPr lang="en-GB"/>
+              <a:t>MSE by Number of Iterations (Gauss-Seidel</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t>y Number Of Iterations (Jacobi)</a:t>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Method)</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -837,7 +663,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Jacobi!$B$1</c:f>
+              <c:f>'Gauss-Seidel'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -856,67 +682,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Jacobi!$A$2:$A$6</c:f>
+              <c:f>'Gauss-Seidel'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -940,38 +708,37 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Jacobi!$B$2:$B$6</c:f>
+              <c:f>'Gauss-Seidel'!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>42.866999999999997</c:v>
+                  <c:v>45.213999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.762999999999998</c:v>
+                  <c:v>58.094999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.674999999999997</c:v>
+                  <c:v>64.718000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>59.201000000000001</c:v>
+                  <c:v>68.376000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62.613</c:v>
+                  <c:v>70.561000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3F47-4F85-B2BC-352F1D23A157}"/>
+              <c16:uniqueId val="{00000000-BFA4-4473-A28D-C9BCE91C6498}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -979,76 +746,16 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="166424991"/>
-        <c:axId val="166427871"/>
+        <c:axId val="365193039"/>
+        <c:axId val="365193519"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="166424991"/>
+        <c:axId val="365193039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Number</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" baseline="0"/>
-                  <a:t> of Iterations</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-GB"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1086,7 +793,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="166427871"/>
+        <c:crossAx val="365193519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1094,7 +801,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="166427871"/>
+        <c:axId val="365193519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1114,61 +821,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Mean Squared Error (MSE)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1200,7 +852,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="166424991"/>
+        <c:crossAx val="365193039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2340,22 +1992,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B535FF5-82F5-368A-7638-767A7CDC0151}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A58024-7644-42FB-7108-22A5644A6853}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2380,23 +2032,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B5A3FC5-ECC3-CBDB-CFC9-BE406EB3FBC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805BE08F-35E6-8C7E-879F-2DDDE52A7D79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2418,25 +2070,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EDA264CB-2371-471F-A5A2-B7046C784E15}" name="Table3" displayName="Table3" ref="A1:B6" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:B6" xr:uid="{EDA264CB-2371-471F-A5A2-B7046C784E15}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ABDFE733-C989-49F7-8179-292652C3A7E5}" name="Number of Iterations" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{652ADC36-38E2-4F11-97DD-67283DBD8B6C}" name="MSE" dataDxfId="4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{76BDDF23-E57D-4860-AE96-3D3AE711E5E3}" name="Table2" displayName="Table2" ref="A1:B6" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:B6" xr:uid="{76BDDF23-E57D-4860-AE96-3D3AE711E5E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B6">
-    <sortCondition ref="B1:B6"/>
-  </sortState>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6B2D9E8B-ECF9-4502-9BE3-9E6793AE7D6C}" name="Number of Iterations" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{274DCDB9-B590-4F29-8207-FF1E8DFEC4A5}" name="MSE" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}" name="Table4" displayName="Table4" ref="A1:C31" totalsRowShown="0" dataDxfId="0">
+  <autoFilter ref="A1:C31" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{8AEA0D4B-E9F5-4567-953A-1D182CFA76F1}" name="Number of Iterations" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1F93E946-D8AD-428A-A0E9-5A7D9F258618}" name="Omega" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{37D41052-D3BF-4893-8BC5-783EDA241B2D}" name="MSE" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2738,137 +2377,429 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51E154B-B520-40B4-8FD5-A3286721D9D2}">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8356F9-7093-4523-A092-C1036B1CDCDE}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="6">
-        <v>45.213999999999999</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="B2" s="4">
+        <v>42.866999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>4</v>
       </c>
-      <c r="B3" s="7">
-        <v>58.094999999999999</v>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="B3" s="5">
+        <v>48.762999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="7">
-        <v>64.718000000000004</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="B4" s="4">
+        <v>54.674999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>8</v>
       </c>
-      <c r="B5" s="7">
-        <v>68.376000000000005</v>
-      </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="B5" s="5">
+        <v>59.201000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
-        <v>70.561000000000007</v>
-      </c>
-      <c r="C6" s="2"/>
+      <c r="B6" s="4">
+        <v>62.613</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB7C7F8-C35B-4306-B386-7BD9C920195C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD715877-BFE9-42BD-9D4F-1C3D61467296}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
-        <v>42.866999999999997</v>
+      <c r="B2" s="7">
+        <v>45.213999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
-        <v>48.762999999999998</v>
+      <c r="B3" s="6">
+        <v>58.094999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
-        <v>54.674999999999997</v>
+      <c r="B4" s="7">
+        <v>64.718000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
-        <v>59.201000000000001</v>
+      <c r="B5" s="6">
+        <v>68.376000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="3">
         <v>10</v>
       </c>
-      <c r="B6" s="1">
-        <v>62.613</v>
+      <c r="B6" s="7">
+        <v>70.561000000000007</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC9FC7C-2A8B-42A3-B61F-B0C00C82015C}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>10</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>10</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>2</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>10</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="C31" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/results/Metrics.xlsx
+++ b/results/Metrics.xlsx
@@ -2,22 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bavra\Desktop\image-unbluring\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254BCF37-35D0-4843-8EE2-72A9515DDEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC81D403-54DC-415C-857A-509D0474D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9E8781EB-8CA8-4CA7-9ABE-25F10890F6BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E8781EB-8CA8-4CA7-9ABE-25F10890F6BB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Jacobi" sheetId="5" r:id="rId1"/>
-    <sheet name="Gauss-Seidel" sheetId="4" r:id="rId2"/>
-    <sheet name="SOR" sheetId="3" r:id="rId3"/>
+    <sheet name="Comparison" sheetId="9" r:id="rId1"/>
+    <sheet name="MSE Data" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="26" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="10">
   <si>
     <t>Number of Iterations</t>
   </si>
@@ -46,23 +48,36 @@
   <si>
     <t>Omega</t>
   </si>
+  <si>
+    <t xml:space="preserve">MSE </t>
+  </si>
+  <si>
+    <t>SOR</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Jacobi</t>
+  </si>
+  <si>
+    <t>Gauss-Seidel</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -74,7 +89,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -83,42 +98,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -138,51 +128,87 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="20">
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -210,6 +236,10 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Metrics.xlsx]Comparison!PivotTable6</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
@@ -232,11 +262,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB"/>
-              <a:t>MSE by</a:t>
+              <a:t>Iterative Algorithm</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" baseline="0"/>
-              <a:t> Number of Iterations (Jacobi Method)</a:t>
+              <a:t> Comparison</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -272,100 +302,573 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Jacobi!$B$1</c:f>
+              <c:f>Comparison!$B$3:$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>MSE</c:v>
+                  <c:v>Gauss-Seidel - 1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Jacobi!$A$2:$A$6</c:f>
+              <c:f>Comparison!$B$6:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>45.213999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.094999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64.718000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.376000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.561000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$C$3:$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Jacobi - -</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -380,12 +883,12 @@
                 <c:pt idx="4">
                   <c:v>10</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Jacobi!$B$2:$B$6</c:f>
+              <c:f>Comparison!$C$6:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -407,9 +910,494 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC81-4861-9A96-97B8CA84C857}"/>
+              <c16:uniqueId val="{00000001-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$D$3:$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 0.25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$D$6:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>55.271999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38.633000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.326999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.131</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38.268999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$E$3:$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 0.5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$E$6:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>36.670999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.591000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43.423000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48.755000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.122999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$F$3:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 0.75</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$F$6:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>36.936999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47.137</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55.012</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60.34</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$G$3:$G$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 1.25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$G$6:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>60.561</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68.900999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71.575000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.974999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73.701999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$H$3:$H$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 1.5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$H$6:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>89.168999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80.313999999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>74.632999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74.423000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-EF48-4975-B4D4-272EB2859A61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$I$3:$I$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOR - 1.75</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$6:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$I$6:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>145.53100000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>103.877</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78.643000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78.997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>77.441000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-EF48-4975-B4D4-272EB2859A61}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -421,13 +1409,12 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="365176239"/>
-        <c:axId val="365191119"/>
-      </c:barChart>
+        <c:smooth val="0"/>
+        <c:axId val="674132960"/>
+        <c:axId val="674128640"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="365176239"/>
+        <c:axId val="674132960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -470,7 +1457,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365191119"/>
+        <c:crossAx val="674128640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -478,7 +1465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365191119"/>
+        <c:axId val="674128640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -529,7 +1516,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365176239"/>
+        <c:crossAx val="674132960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -541,9 +1528,47 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -575,329 +1600,21 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t>MSE by Number of Iterations (Gauss-Seidel</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-GB" baseline="0"/>
-              <a:t> Method)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Gauss-Seidel'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>MSE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Gauss-Seidel'!$A$2:$A$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Gauss-Seidel'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>45.213999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>58.094999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64.718000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68.376000000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>70.561000000000007</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BFA4-4473-A28D-C9BCE91C6498}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="365193039"/>
-        <c:axId val="365193519"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="365193039"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="365193519"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="365193519"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="365193039"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -941,48 +1658,8 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1090,6 +1767,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1100,6 +1782,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1131,509 +1818,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1991,23 +2178,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A58024-7644-42FB-7108-22A5644A6853}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C16938E8-E10A-AB63-7196-40FB6D636314}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2028,54 +2215,613 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805BE08F-35E6-8C7E-879F-2DDDE52A7D79}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bill Avramidis" refreshedDate="46034.880809490744" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{2D800FBF-3192-4FAA-9068-807472246200}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table4"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Number of Iterations" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="10" count="5">
+        <n v="2"/>
+        <n v="4"/>
+        <n v="6"/>
+        <n v="8"/>
+        <n v="10"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Omega" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0.25" maxValue="1.75" count="8">
+        <n v="0.25"/>
+        <n v="0.5"/>
+        <n v="0.75"/>
+        <n v="1.25"/>
+        <n v="1.5"/>
+        <n v="1.75"/>
+        <s v="-"/>
+        <n v="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="MSE" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35.326999999999998" maxValue="145.53100000000001"/>
+    </cacheField>
+    <cacheField name="Method" numFmtId="0">
+      <sharedItems count="3">
+        <s v="SOR"/>
+        <s v="Jacobi"/>
+        <s v="Gauss-Seidel"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="55.271999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="38.633000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="35.326999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="36.131"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="38.268999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="36.670999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="37.591000000000001"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="43.423000000000002"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="48.755000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="53.122999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="36.936999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="47.137"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="55.012"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="60.34"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="64.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="60.561"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="68.900999999999996"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="71.575000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="72.974999999999994"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="73.701999999999998"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="89.168999999999997"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="80.313999999999993"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="74.632999999999996"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="74.423000000000002"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="74.44"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="145.53100000000001"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="103.877"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="78.643000000000001"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="78.997"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="77.441000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="42.866999999999997"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="48.762999999999998"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="54.674999999999997"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="59.201000000000001"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="62.613"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="45.213999999999999"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="58.094999999999999"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="64.718000000000004"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="68.376000000000005"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="70.561000000000007"/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6591FF45-E36F-4C0E-B808-3890A37B2998}" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Number of Iterations" colHeaderCaption="Methods">
+  <location ref="A3:I10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="3"/>
+    <field x="1"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="MSE " fld="2" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="13">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="1">
+            <x v="7"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="1" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}" name="Table4" displayName="Table4" ref="A1:C31" totalsRowShown="0" dataDxfId="0">
-  <autoFilter ref="A1:C31" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8AEA0D4B-E9F5-4567-953A-1D182CFA76F1}" name="Number of Iterations" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{1F93E946-D8AD-428A-A0E9-5A7D9F258618}" name="Omega" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{37D41052-D3BF-4893-8BC5-783EDA241B2D}" name="MSE" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}" name="Table4" displayName="Table4" ref="A1:D41" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:D41" xr:uid="{2A0FDFCD-92AA-4DA1-BF45-B6DD841345FD}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8AEA0D4B-E9F5-4567-953A-1D182CFA76F1}" name="Number of Iterations" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{1F93E946-D8AD-428A-A0E9-5A7D9F258618}" name="Omega" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{37D41052-D3BF-4893-8BC5-783EDA241B2D}" name="MSE" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E6357A06-BEB4-4FAB-AAF3-426558A9B623}" name="Method" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2377,426 +3123,819 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8356F9-7093-4523-A092-C1036B1CDCDE}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD23C4AB-34D3-4EFE-8648-8215321BD94B}">
+  <dimension ref="A3:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B6" s="5">
+        <v>45.213999999999999</v>
+      </c>
+      <c r="C6" s="5">
         <v>42.866999999999997</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="D6" s="5">
+        <v>55.271999999999998</v>
+      </c>
+      <c r="E6" s="5">
+        <v>36.670999999999999</v>
+      </c>
+      <c r="F6" s="5">
+        <v>36.936999999999998</v>
+      </c>
+      <c r="G6" s="5">
+        <v>60.561</v>
+      </c>
+      <c r="H6" s="5">
+        <v>89.168999999999997</v>
+      </c>
+      <c r="I6" s="5">
+        <v>145.53100000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B7" s="5">
+        <v>58.094999999999999</v>
+      </c>
+      <c r="C7" s="5">
         <v>48.762999999999998</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="D7" s="5">
+        <v>38.633000000000003</v>
+      </c>
+      <c r="E7" s="5">
+        <v>37.591000000000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>47.137</v>
+      </c>
+      <c r="G7" s="5">
+        <v>68.900999999999996</v>
+      </c>
+      <c r="H7" s="5">
+        <v>80.313999999999993</v>
+      </c>
+      <c r="I7" s="5">
+        <v>103.877</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B8" s="5">
+        <v>64.718000000000004</v>
+      </c>
+      <c r="C8" s="5">
         <v>54.674999999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="D8" s="5">
+        <v>35.326999999999998</v>
+      </c>
+      <c r="E8" s="5">
+        <v>43.423000000000002</v>
+      </c>
+      <c r="F8" s="5">
+        <v>55.012</v>
+      </c>
+      <c r="G8" s="5">
+        <v>71.575000000000003</v>
+      </c>
+      <c r="H8" s="5">
+        <v>74.632999999999996</v>
+      </c>
+      <c r="I8" s="5">
+        <v>78.643000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B9" s="5">
+        <v>68.376000000000005</v>
+      </c>
+      <c r="C9" s="5">
         <v>59.201000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="D9" s="5">
+        <v>36.131</v>
+      </c>
+      <c r="E9" s="5">
+        <v>48.755000000000003</v>
+      </c>
+      <c r="F9" s="5">
+        <v>60.34</v>
+      </c>
+      <c r="G9" s="5">
+        <v>72.974999999999994</v>
+      </c>
+      <c r="H9" s="5">
+        <v>74.423000000000002</v>
+      </c>
+      <c r="I9" s="5">
+        <v>78.997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B10" s="5">
+        <v>70.561000000000007</v>
+      </c>
+      <c r="C10" s="5">
         <v>62.613</v>
+      </c>
+      <c r="D10" s="5">
+        <v>38.268999999999998</v>
+      </c>
+      <c r="E10" s="5">
+        <v>53.122999999999998</v>
+      </c>
+      <c r="F10" s="5">
+        <v>64.02</v>
+      </c>
+      <c r="G10" s="5">
+        <v>73.701999999999998</v>
+      </c>
+      <c r="H10" s="5">
+        <v>74.44</v>
+      </c>
+      <c r="I10" s="5">
+        <v>77.441000000000003</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD715877-BFE9-42BD-9D4F-1C3D61467296}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7">
-        <v>45.213999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6">
-        <v>58.094999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>6</v>
-      </c>
-      <c r="B4" s="7">
-        <v>64.718000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6">
-        <v>68.376000000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>10</v>
-      </c>
-      <c r="B6" s="7">
-        <v>70.561000000000007</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC9FC7C-2A8B-42A3-B61F-B0C00C82015C}">
-  <dimension ref="A1:C31"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2</v>
       </c>
       <c r="B2" s="1">
         <v>0.25</v>
       </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" s="2">
+        <v>55.271999999999998</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>0.25</v>
       </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" s="3">
+        <v>38.633000000000003</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>0.25</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="2">
+        <v>35.326999999999998</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>0.25</v>
       </c>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <v>36.131</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>10</v>
       </c>
       <c r="B6" s="1">
         <v>0.25</v>
       </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <v>38.268999999999998</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" s="1">
         <v>0.5</v>
       </c>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7" s="1">
+        <v>36.670999999999999</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>0.5</v>
       </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" s="1">
+        <v>37.591000000000001</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1">
         <v>0.5</v>
       </c>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
+        <v>43.423000000000002</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>0.5</v>
       </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>48.755000000000003</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>0.5</v>
       </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
+        <v>53.122999999999998</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="1">
         <v>0.75</v>
       </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
+        <v>36.936999999999998</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>4</v>
       </c>
       <c r="B13" s="1">
         <v>0.75</v>
       </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C13" s="1">
+        <v>47.137</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6</v>
       </c>
       <c r="B14" s="1">
         <v>0.75</v>
       </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C14" s="1">
+        <v>55.012</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>8</v>
       </c>
       <c r="B15" s="1">
         <v>0.75</v>
       </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C15" s="1">
+        <v>60.34</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>10</v>
       </c>
       <c r="B16" s="1">
         <v>0.75</v>
       </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" s="1">
+        <v>64.02</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="1">
         <v>1.25</v>
       </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="1">
+        <v>60.561</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>4</v>
       </c>
       <c r="B18" s="1">
         <v>1.25</v>
       </c>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="1">
+        <v>68.900999999999996</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>6</v>
       </c>
       <c r="B19" s="1">
         <v>1.25</v>
       </c>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C19" s="1">
+        <v>71.575000000000003</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>8</v>
       </c>
       <c r="B20" s="1">
         <v>1.25</v>
       </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="1">
+        <v>72.974999999999994</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>10</v>
       </c>
       <c r="B21" s="1">
         <v>1.25</v>
       </c>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="1">
+        <v>73.701999999999998</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
       <c r="B22" s="1">
         <v>1.5</v>
       </c>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="1">
+        <v>89.168999999999997</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="1">
         <v>1.5</v>
       </c>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="1">
+        <v>80.313999999999993</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>6</v>
       </c>
       <c r="B24" s="1">
         <v>1.5</v>
       </c>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="1">
+        <v>74.632999999999996</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>8</v>
       </c>
       <c r="B25" s="1">
         <v>1.5</v>
       </c>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="1">
+        <v>74.423000000000002</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>10</v>
       </c>
       <c r="B26" s="1">
         <v>1.5</v>
       </c>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="1">
+        <v>74.44</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>2</v>
       </c>
       <c r="B27" s="1">
         <v>1.75</v>
       </c>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="1">
+        <v>145.53100000000001</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="1">
         <v>1.75</v>
       </c>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C28" s="1">
+        <v>103.877</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>6</v>
       </c>
       <c r="B29" s="1">
         <v>1.75</v>
       </c>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="1">
+        <v>78.643000000000001</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>8</v>
       </c>
       <c r="B30" s="1">
         <v>1.75</v>
       </c>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C30" s="1">
+        <v>78.997</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>10</v>
       </c>
       <c r="B31" s="1">
         <v>1.75</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>77.441000000000003</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>2</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>42.866999999999997</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>48.762999999999998</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1">
+        <v>54.674999999999997</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>8</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1">
+        <v>59.201000000000001</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1">
+        <v>62.613</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>2</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>45.213999999999999</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>58.094999999999999</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>64.718000000000004</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>8</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1">
+        <v>68.376000000000005</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>10</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>70.561000000000007</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/results/Metrics.xlsx
+++ b/results/Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bavra\Desktop\image-unbluring\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC81D403-54DC-415C-857A-509D0474D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B842B04-CC2E-41FD-8A8C-DF1F3862B6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E8781EB-8CA8-4CA7-9ABE-25F10890F6BB}"/>
   </bookViews>
